--- a/每日输出/初短二部/郑州-初短二部-销售风灵在线率明细数据.xlsx
+++ b/每日输出/初短二部/郑州-初短二部-销售风灵在线率明细数据.xlsx
@@ -613,32 +613,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688857858819005</t>
+          <t>1688856037696790</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>余露</t>
+          <t>薛佳蕊</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>yulu</t>
+          <t>xuejiarui</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -650,7 +650,12 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -692,7 +697,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688856037697599</t>
+          <t>1688857166896046,1688854991811096</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -702,22 +707,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>以梦为马</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>刘松</t>
+          <t>宋美璇</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>liusong01</t>
+          <t>songmeixuan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -776,32 +781,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688856125906724</t>
+          <t>1688856390786235</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>新兵营恩</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>丁晓</t>
+          <t>刘路菲</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>dingxiao01</t>
+          <t>liulufei</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -860,32 +865,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688856737815838</t>
+          <t>1688856725902364</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>新兵营恩</t>
+          <t>骏成必燃</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>靳恩慧</t>
+          <t>王怡涵</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>jinenhui</t>
+          <t>wangyihan02</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -944,32 +949,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688858343817177</t>
+          <t>1688855795758409</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>潘英杰</t>
+          <t>胡铭</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>panyingjie</t>
+          <t>huming</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1023,32 +1028,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854464789112</t>
+          <t>1688857359851226</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>陈帅</t>
+          <t>梅思莹</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>chenshuai02</t>
+          <t>meisiying</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1060,12 +1065,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1107,32 +1107,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688857322827364</t>
+          <t>1688854264827703</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>段瑶</t>
+          <t>孟鑫</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>duanyao</t>
+          <t>mengxin</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,32 +1191,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688856018811331</t>
+          <t>1688856037697222</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>李浩毅</t>
+          <t>毛宁</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lihaoyi</t>
+          <t>maoning</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1228,11 +1228,11 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1275,32 +1275,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688855137874728</t>
+          <t>1688854551837457</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>新兵营潇</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>孙之涵</t>
+          <t>郭亚东</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>sunzhihan</t>
+          <t>guoyadong</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688855248814365</t>
+          <t>1688856902888900</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1369,22 +1369,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>徐安平</t>
+          <t>鲁冰洁</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>xuanping</t>
+          <t>lubingjie</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1393,12 +1393,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1409,12 +1404,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1453,32 +1443,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688854337826449</t>
+          <t>1688854397763552</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>王海英</t>
+          <t>张子涵</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>wanghaiying</t>
+          <t>zhangzihan03</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1493,7 +1483,12 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1532,7 +1527,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688856003795305</t>
+          <t>1688856859841723</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1542,22 +1537,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>李鼎</t>
+          <t>闫琳琳</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>liding02</t>
+          <t>yanlinlin</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1572,7 +1567,12 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1611,32 +1611,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688858020842485</t>
+          <t>1688858314771997</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>以梦为马</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>叶杲昂</t>
+          <t>王玉章</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>yegaoang</t>
+          <t>wangyuzhang</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1645,12 +1645,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1661,12 +1656,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1705,32 +1695,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688857633792974</t>
+          <t>1688858319891945</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>陈振宇</t>
+          <t>张鹏威</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>chenzhenyu</t>
+          <t>zhangpengwei</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1789,32 +1779,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688856204843386</t>
+          <t>1688856475868232</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>王文娟</t>
+          <t>冯茹冰</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>wangwenjuan</t>
+          <t>fengrubing</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1873,32 +1863,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688858427814586</t>
+          <t>1688856037696692</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>以梦为马</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>王艺博</t>
+          <t>刘琦</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>wangyibo02</t>
+          <t>liuqi</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1910,11 +1900,11 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -1957,7 +1947,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688856891776212</t>
+          <t>1688857525700825</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1967,22 +1957,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>苏志颖</t>
+          <t>朱龙飞</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suzhiying</t>
+          <t>zhulongfei01</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1994,12 +1984,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -2041,7 +2026,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688857961849908</t>
+          <t>1688858109824482</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2051,22 +2036,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>师雅晶</t>
+          <t>王亚婷</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>shiyajing</t>
+          <t>wangyating</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2078,12 +2063,7 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -2125,32 +2105,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688854454768346</t>
+          <t>1688857582835317</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>骏成必燃</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>贾军慧</t>
+          <t>李博</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>jiajunhui</t>
+          <t>libo03</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2162,12 +2142,7 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
@@ -2209,7 +2184,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688856891776048</t>
+          <t>1688855978877650</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2219,22 +2194,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>杨海珍</t>
+          <t>冯欣颖</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>yanghaizhen</t>
+          <t>fengxinying</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2246,7 +2221,12 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
@@ -2288,7 +2268,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688857053845790</t>
+          <t>1688857143879139</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2298,22 +2278,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>刘源</t>
+          <t>高佳梦</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>liuyuan02</t>
+          <t>gaojiameng</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2372,7 +2352,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688856859841723</t>
+          <t>1688854264828019</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2382,22 +2362,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>闫琳琳</t>
+          <t>韩露露</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>yanlinlin</t>
+          <t>hanlulu</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2409,7 +2389,12 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,21,22,23</t>
+        </is>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -2451,32 +2436,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688854662883948</t>
+          <t>1688856891776091</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>新兵营潇</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>程志豪</t>
+          <t>唐致鹏</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>chengzhihao</t>
+          <t>tangzhipeng</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2535,32 +2520,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688856929827524</t>
+          <t>1688856037697255</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>栗亚楠</t>
+          <t>高丽静</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>liyanan03</t>
+          <t>gaolijing</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2572,12 +2557,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
@@ -2619,7 +2599,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688857905847066</t>
+          <t>1688858040865576</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2629,22 +2609,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>马艺铭</t>
+          <t>苏妍</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>mayiming</t>
+          <t>suyan</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2656,7 +2636,12 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
@@ -2698,32 +2683,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688855954888267</t>
+          <t>1688854464789088</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>新兵营恩</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>姬世杰</t>
+          <t>李依航</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>jishijie</t>
+          <t>liyihang</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2782,7 +2767,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688857176811450</t>
+          <t>1688855363865970</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2792,22 +2777,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>李洪翔</t>
+          <t>赵怡琳</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>lihongxiang</t>
+          <t>zhaoyilin01</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2866,7 +2851,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688856037697362</t>
+          <t>1688857792756340</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2881,17 +2866,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>刘晓雨</t>
+          <t>王志伟</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>liuxiaoyu</t>
+          <t>wangzhiwei</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2900,28 +2885,13 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -2960,32 +2930,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688857961850111</t>
+          <t>1688856003795286</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>高林林</t>
+          <t>刘明慧</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>gaolinlin</t>
+          <t>liuminghui</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2994,28 +2964,13 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3054,32 +3009,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688856018811229</t>
+          <t>1688858040865374</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>驰野逐光</t>
+          <t>新兵营学</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>闫肃</t>
+          <t>卢雅琦</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>yansu</t>
+          <t>luyaqi</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3091,7 +3046,12 @@
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
@@ -3133,7 +3093,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688855248814582</t>
+          <t>1688858136775217</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3143,22 +3103,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>张雪</t>
+          <t>陈浩</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zhangxue01</t>
+          <t>chenhao01</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3170,12 +3130,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -3217,7 +3172,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688854452785935</t>
+          <t>1688856211774153</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3232,17 +3187,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>王逸凡</t>
+          <t>赵杨</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>wangyifan05</t>
+          <t>zhaoyang01</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3301,32 +3256,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688854398842366</t>
+          <t>1688855498794139</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>张豫龙</t>
+          <t>苏免冰</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zhangyulong</t>
+          <t>sumianbing</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3338,12 +3293,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -3385,7 +3335,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688858040865834</t>
+          <t>1688857961849908</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3395,22 +3345,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>徐沛鸽</t>
+          <t>师雅晶</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>xupeige</t>
+          <t>shiyajing</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3469,7 +3419,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688856003795286</t>
+          <t>1688854415798586</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3479,22 +3429,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>刘明慧</t>
+          <t>张勋</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>liuminghui</t>
+          <t>zhangxun</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3506,7 +3456,12 @@
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3548,7 +3503,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688857961849964</t>
+          <t>1688856018811229</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3558,22 +3513,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>驰野逐光</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>李静怡</t>
+          <t>闫肃</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>lijingyi02</t>
+          <t>yansu</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3627,7 +3582,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688857832838680</t>
+          <t>1688855137874873</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3637,22 +3592,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>杜晓宁</t>
+          <t>裴珊珊</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>duxiaoning</t>
+          <t>peishanshan</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3711,7 +3666,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688856037697222</t>
+          <t>1688856037697156</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3721,22 +3676,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>毛宁</t>
+          <t>王迪</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>maoning</t>
+          <t>wangdi01</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3748,7 +3703,12 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -3790,32 +3750,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688856891776282</t>
+          <t>1688855788797719</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>骏成必燃</t>
+          <t>新兵营学</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>侯典飞</t>
+          <t>李博文</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>houdianfei</t>
+          <t>libowen</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3874,7 +3834,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688856737815864</t>
+          <t>1688857702013332</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3884,22 +3844,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>杨迪</t>
+          <t>郭嘉欣</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>yangdi</t>
+          <t>guojiaxin01</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3908,12 +3868,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3924,12 +3879,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -3968,32 +3918,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688856725902373</t>
+          <t>1688854454768346</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>新兵营恩</t>
+          <t>骏成必燃</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>崔振</t>
+          <t>贾军慧</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>cuizhen01</t>
+          <t>jiajunhui</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4052,32 +4002,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688856891776267</t>
+          <t>1688856891776282</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>骏成必燃</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>郑雨萌</t>
+          <t>侯典飞</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zhengyumeng</t>
+          <t>houdianfei</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4089,7 +4039,12 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
@@ -4131,7 +4086,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688854454768334</t>
+          <t>1688858343817137</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4141,22 +4096,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>骏成必燃</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>郭家发</t>
+          <t>凌艺萌</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>guojiafa</t>
+          <t>lingyimeng</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4168,11 +4123,11 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -4215,32 +4170,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688857961849923</t>
+          <t>1688857154905626</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>新兵营潇</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>张智博</t>
+          <t>张磊磊</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>zhangzhibo</t>
+          <t>zhangleilei02</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4252,7 +4207,12 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -4294,32 +4254,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688856396700606</t>
+          <t>1688856204843386</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>和孟晴</t>
+          <t>王文娟</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>hemengqing</t>
+          <t>wangwenjuan</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4331,11 +4291,11 @@
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>17,18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -4378,32 +4338,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688856037697255</t>
+          <t>1688855156825040</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>高丽静</t>
+          <t>赵晓旭</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>gaolijing</t>
+          <t>zhaoxiaoxu</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4415,7 +4375,12 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
@@ -4457,7 +4422,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688856339696459</t>
+          <t>1688857961850111</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4467,22 +4432,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>车则龙</t>
+          <t>高林林</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>chezelong</t>
+          <t>gaolinlin</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4494,7 +4459,12 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -4536,32 +4506,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688856037697156</t>
+          <t>1688854324738394</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>王迪</t>
+          <t>彭培鑫</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>wangdi01</t>
+          <t>pengpeixin</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4570,27 +4540,27 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>22,23</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,22,23</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>21,22,23</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -4630,32 +4600,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688855201870266</t>
+          <t>1688854678837505</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>李申申</t>
+          <t>赵赫</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lishenshen</t>
+          <t>zhaohe</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4667,12 +4637,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
@@ -4714,32 +4679,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688856735809161</t>
+          <t>1688854264827964</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>崔梓慧</t>
+          <t>张琳琳</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>cuizihui</t>
+          <t>zhanglinlin01</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4751,12 +4716,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4798,32 +4758,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688857108697470</t>
+          <t>1688857322827364</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>党晓磊</t>
+          <t>段瑶</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>dangxiaolei</t>
+          <t>duanyao</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4832,13 +4792,28 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -4877,32 +4852,32 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688856037696887</t>
+          <t>1688854337826449</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>王英颖</t>
+          <t>王海英</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>wangyingying03</t>
+          <t>wanghaiying</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4914,12 +4889,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -4961,32 +4931,32 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688855156825040</t>
+          <t>1688854373723255</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>以梦为马</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>赵晓旭</t>
+          <t>张世豪</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zhaoxiaoxu</t>
+          <t>zhangshihao</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5045,32 +5015,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688856902888900</t>
+          <t>1688856891776267</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>鲁冰洁</t>
+          <t>郑雨萌</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>lubingjie</t>
+          <t>zhengyumeng</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5082,12 +5052,7 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
@@ -5129,32 +5094,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688857582835317</t>
+          <t>1688856737815864</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>李博</t>
+          <t>杨迪</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>libo03</t>
+          <t>yangdi</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5166,7 +5131,12 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
@@ -5208,32 +5178,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688858319891964</t>
+          <t>1688856842821046</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>新兵营学</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>闫月</t>
+          <t>叶肖跃</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>yanyue01</t>
+          <t>yexiaoyue</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5292,32 +5262,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688857696798168</t>
+          <t>1688856891776048</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>以梦为马</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>刘梦颖</t>
+          <t>杨海珍</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>liumengying</t>
+          <t>yanghaizhen</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5371,32 +5341,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688858319892207</t>
+          <t>1688858343817177</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>何晶晶</t>
+          <t>潘英杰</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>hejingjing</t>
+          <t>panyingjie</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5408,11 +5378,11 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>6,7,8,9,10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -5455,32 +5425,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688858040865739</t>
+          <t>1688854397763587</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>驰野逐光</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>朱智凤</t>
+          <t>万亚朋</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zhuzhifeng</t>
+          <t>wanyapeng</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5539,32 +5509,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688858319891945</t>
+          <t>1688855201870266</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>张鹏威</t>
+          <t>李申申</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhangpengwei</t>
+          <t>lishenshen</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5623,32 +5593,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688856475868803</t>
+          <t>1688855788797704</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>杜亚柯</t>
+          <t>王超杰</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>duyake</t>
+          <t>wangchaojie01</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5707,7 +5677,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688856037696815</t>
+          <t>1688854398842366</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5717,22 +5687,22 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>赵毅</t>
+          <t>张豫龙</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zhaoyi</t>
+          <t>zhangyulong</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5744,7 +5714,12 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
@@ -5786,32 +5761,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688856189837742</t>
+          <t>1688855137874728</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>新兵营潇</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>薛雨</t>
+          <t>孙之涵</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>xueyu</t>
+          <t>sunzhihan</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5870,7 +5845,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688855795758382</t>
+          <t>1688857176811450</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5880,22 +5855,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>陈慧</t>
+          <t>李洪翔</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>chenhui</t>
+          <t>lihongxiang</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5907,7 +5882,12 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
@@ -5949,7 +5929,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688854415798586</t>
+          <t>1688855236782129</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5959,22 +5939,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>张勋</t>
+          <t>刘苗苗</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zhangxun</t>
+          <t>liumiaomiao</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6033,7 +6013,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688854264827703</t>
+          <t>1688855161843005</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6043,22 +6023,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>孟鑫</t>
+          <t>王善岩</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>mengxin</t>
+          <t>wangshanyan</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6070,12 +6050,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
@@ -6117,32 +6092,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688854292962247</t>
+          <t>1688856891776337</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>翟伊蕊</t>
+          <t>胡志超</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>zhaiyirui</t>
+          <t>huzhichao</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6201,7 +6176,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688856037696692</t>
+          <t>1688857633792974</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6211,22 +6186,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>刘琦</t>
+          <t>陈振宇</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>liuqi</t>
+          <t>chenzhenyu</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6238,7 +6213,12 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
@@ -6280,32 +6260,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688856475868232</t>
+          <t>1688857108697470</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>冯茹冰</t>
+          <t>党晓磊</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>fengrubing</t>
+          <t>dangxiaolei</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6317,12 +6297,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
@@ -6364,7 +6339,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688854324738394</t>
+          <t>1688856037697599</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6374,22 +6349,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>彭培鑫</t>
+          <t>刘松</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>pengpeixin</t>
+          <t>liusong01</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6448,32 +6423,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688856842821046</t>
+          <t>1688855795758464</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>叶肖跃</t>
+          <t>王惠惠</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>yexiaoyue</t>
+          <t>wanghuihui01</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6532,7 +6507,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688855564781029</t>
+          <t>1688854275802397</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6542,22 +6517,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>陈文强</t>
+          <t>韩宜甫</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>chenwenqiang</t>
+          <t>hanyifu</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6569,7 +6544,12 @@
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
@@ -6611,32 +6591,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688854551837457</t>
+          <t>1688856037696984</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>郭亚东</t>
+          <t>李慧婷</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>guoyadong</t>
+          <t>lihuiting</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6648,12 +6628,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
@@ -6695,32 +6670,32 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688858343816603</t>
+          <t>1688856737815887</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>冉晓瀚</t>
+          <t>王佳</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ranxiaohan</t>
+          <t>wangjia02</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6774,7 +6749,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688854551837425</t>
+          <t>1688858040865739</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6784,22 +6759,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>张志涵</t>
+          <t>朱智凤</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>zhangzhihan</t>
+          <t>zhuzhifeng</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6858,32 +6833,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688855137874873</t>
+          <t>1688855795758522</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>裴珊珊</t>
+          <t>刘茹月</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>peishanshan</t>
+          <t>liuruyue</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6895,11 +6870,11 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q77" t="n">
@@ -6942,32 +6917,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688858040865374</t>
+          <t>1688856125906724</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>新兵营学</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>卢雅琦</t>
+          <t>丁晓</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>luyaqi</t>
+          <t>dingxiao01</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7026,32 +7001,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688855795758509</t>
+          <t>1688855795758484</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>新兵营学</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>马礼君</t>
+          <t>孙博学</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>malijun</t>
+          <t>sunboxue</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7105,7 +7080,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688856819815544</t>
+          <t>1688856929827524</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7115,22 +7090,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>安文杰</t>
+          <t>栗亚楠</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>anwenjie</t>
+          <t>liyanan03</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7142,7 +7117,12 @@
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -7184,7 +7164,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688854373723255</t>
+          <t>1688855248814592</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7199,17 +7179,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>张世豪</t>
+          <t>刘岩</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>zhangshihao</t>
+          <t>liuyan01</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7268,32 +7248,32 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688857525700825</t>
+          <t>1688854337826427</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>朱龙飞</t>
+          <t>余梦真</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>zhulongfei01</t>
+          <t>yumengzhen</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7305,7 +7285,12 @@
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
@@ -7347,32 +7332,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688858435677635</t>
+          <t>1688856003795391</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>赵庆澳</t>
+          <t>王春荷</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>zhaoqingao</t>
+          <t>wangchunhe</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7384,12 +7369,7 @@
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
         <v>1</v>
@@ -7431,32 +7411,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688856003795391</t>
+          <t>1688854551837425</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>王春荷</t>
+          <t>张志涵</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>wangchunhe</t>
+          <t>zhangzhihan</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7468,7 +7448,12 @@
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
@@ -7510,32 +7495,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688856891776337</t>
+          <t>1688857961849964</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>胡志超</t>
+          <t>李静怡</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>huzhichao</t>
+          <t>lijingyi02</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7547,12 +7532,7 @@
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
         <v>1</v>
@@ -7594,7 +7574,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688854275802397</t>
+          <t>1688856324777001</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7604,22 +7584,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>韩宜甫</t>
+          <t>马睿</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>hanyifu</t>
+          <t>marui02</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7631,12 +7611,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
         <v>1</v>
@@ -7678,32 +7653,32 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688856339696430</t>
+          <t>1688858126859815</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>新兵营潇</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>刘士莹</t>
+          <t>晋馨贝</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>liushiying</t>
+          <t>jinxinbei</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7718,7 +7693,12 @@
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -7757,32 +7737,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1688854464789088</t>
+          <t>1688856819815544</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>新兵营恩</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>李依航</t>
+          <t>安文杰</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>liyihang</t>
+          <t>anwenjie</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7794,12 +7774,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
         <v>1</v>
@@ -7841,7 +7816,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1688856037696790</t>
+          <t>1688855248814582</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7851,22 +7826,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>薛佳蕊</t>
+          <t>张雪</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>xuejiarui</t>
+          <t>zhangxue01</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7925,7 +7900,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1688854264828035</t>
+          <t>1688855161842920</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7935,22 +7910,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>驰野逐光</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>刘丰硕</t>
+          <t>郭苏敏</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>liufengshuo</t>
+          <t>guosumin</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7962,12 +7937,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
         <v>1</v>
@@ -8009,32 +7979,32 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1688858109824482</t>
+          <t>1688858435677731</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>王亚婷</t>
+          <t>马平平</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>wangyating</t>
+          <t>mapingping</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8046,7 +8016,12 @@
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q91" t="n">
         <v>1</v>
@@ -8088,32 +8063,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1688855795758522</t>
+          <t>1688858343816603</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>刘茹月</t>
+          <t>冉晓瀚</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>liuruyue</t>
+          <t>ranxiaohan</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8125,12 +8100,7 @@
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
@@ -8172,32 +8142,32 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1688857792756312</t>
+          <t>1688854264828035</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>驰野逐光</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>赵光力</t>
+          <t>刘丰硕</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>zhaoguangli</t>
+          <t>liufengshuo</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8256,32 +8226,32 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1688855535814875</t>
+          <t>1688856740829087</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>驰野逐光</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>陈庆晗</t>
+          <t>刘悦</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>chenqinghan</t>
+          <t>liuyue07</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8340,32 +8310,32 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1688855236782129</t>
+          <t>1688856737815838</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>新兵营恩</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>刘苗苗</t>
+          <t>靳恩慧</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>liumiaomiao</t>
+          <t>jinenhui</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8424,32 +8394,32 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1688854264827893</t>
+          <t>1688855564781029</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>尚林莹</t>
+          <t>陈文强</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>shanglinying</t>
+          <t>chenwenqiang</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8503,32 +8473,32 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1688857143879139</t>
+          <t>1688856390786351</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>高佳梦</t>
+          <t>李佳慧</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>gaojiameng</t>
+          <t>lijiahui03</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8540,12 +8510,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q97" t="n">
         <v>1</v>
@@ -8587,32 +8552,32 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1688856037697403</t>
+          <t>1688856735809161</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>王岳</t>
+          <t>崔梓慧</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>wangyue</t>
+          <t>cuizihui</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8671,7 +8636,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1688857702013332</t>
+          <t>1688856475868803</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8681,22 +8646,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>郭嘉欣</t>
+          <t>杜亚柯</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>guojiaxin01</t>
+          <t>duyake</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8755,32 +8720,32 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1688855031888570</t>
+          <t>1688855795758468</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>骏成必燃</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>郭成</t>
+          <t>许珂</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>guocheng</t>
+          <t>xuke</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8792,12 +8757,7 @@
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q100" t="n">
         <v>1</v>
@@ -8839,7 +8799,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1688855788797704</t>
+          <t>1688857053845790</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8849,22 +8809,22 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>王超杰</t>
+          <t>刘源</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>wangchaojie01</t>
+          <t>liuyuan02</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8923,32 +8883,32 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1688855795758484</t>
+          <t>1688857475803068</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>新兵营学</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>孙博学</t>
+          <t>刘素华</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>sunboxue</t>
+          <t>liusuhua</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9002,32 +8962,32 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1688857704812502</t>
+          <t>1688855795758509</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>刘博雅</t>
+          <t>马礼君</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>liuboya</t>
+          <t>malijun</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9081,32 +9041,32 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1688857053845851</t>
+          <t>1688856037696967</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>驰野逐光</t>
+          <t>骏成必燃</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>李洪仲</t>
+          <t>刘俊杰</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>lihongzhong</t>
+          <t>liujunjie</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9165,32 +9125,32 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1688855498794139</t>
+          <t>1688854452785935</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>新兵营学</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>苏免冰</t>
+          <t>王逸凡</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>sumianbing</t>
+          <t>wangyifan05</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9202,11 +9162,11 @@
         <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q105" t="n">
@@ -9249,32 +9209,32 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1688857475803068</t>
+          <t>1688858040865834</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>刘素华</t>
+          <t>徐沛鸽</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>liusuhua</t>
+          <t>xupeige</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9286,11 +9246,11 @@
         <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>8,9,10</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -9333,32 +9293,32 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1688856341913737</t>
+          <t>1688855954888267</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>新兵营潇</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>高新浩</t>
+          <t>姬世杰</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>gaoxinhao</t>
+          <t>jishijie</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9417,32 +9377,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1688855954887704</t>
+          <t>1688857702013211</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>新兵营学</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>姚庄蔚</t>
+          <t>焦慧瑛</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>yaozhuangwei</t>
+          <t>jiaohuiying</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9451,7 +9411,12 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -9462,7 +9427,12 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -9501,32 +9471,32 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1688855161843005</t>
+          <t>1688855535814875</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>王善岩</t>
+          <t>陈庆晗</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>wangshanyan</t>
+          <t>chenqinghan</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9538,7 +9508,12 @@
         <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q109" t="n">
         <v>1</v>
@@ -9580,32 +9555,32 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1688858343817137</t>
+          <t>1688856037697362</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>凌艺萌</t>
+          <t>刘晓雨</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>lingyimeng</t>
+          <t>liuxiaoyu</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9617,7 +9592,12 @@
         <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
@@ -9659,32 +9639,32 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1688858400836966</t>
+          <t>1688854464789112</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>李柄呈</t>
+          <t>陈帅</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>libingcheng</t>
+          <t>chenshuai02</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9743,32 +9723,32 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1688856749818173</t>
+          <t>1688854452775201</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>新兵营恩</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>孙兵佳</t>
+          <t>张妍</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>sunbingjia</t>
+          <t>zhangyan06</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9780,7 +9760,12 @@
         <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q112" t="n">
         <v>1</v>
@@ -9822,32 +9807,32 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1688858314771997</t>
+          <t>1688857370752824</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>以梦为马</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>王玉章</t>
+          <t>杜宁宁</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>wangyuzhang</t>
+          <t>duningning</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9856,28 +9841,13 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -9916,32 +9886,32 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1688857166896032</t>
+          <t>1688857226802392</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>以梦为马</t>
+          <t>新兵营恩</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>张亚雪</t>
+          <t>崔豪杰</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>zhangyaxue</t>
+          <t>cuihaojie</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9953,7 +9923,12 @@
         <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q114" t="n">
         <v>1</v>
@@ -9995,7 +9970,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1688856037697547</t>
+          <t>1688858427814586</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10005,22 +9980,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>以梦为马</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>张佳慧</t>
+          <t>王艺博</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>zhangjiahui01</t>
+          <t>wangyibo02</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10032,7 +10007,12 @@
         <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q115" t="n">
         <v>1</v>
@@ -10074,7 +10054,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1688856324777001</t>
+          <t>1688858319892207</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -10084,22 +10064,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>马睿</t>
+          <t>何晶晶</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>marui02</t>
+          <t>hejingjing</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10111,7 +10091,12 @@
         <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>16,17</t>
+        </is>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
@@ -10153,32 +10138,32 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1688856211774153</t>
+          <t>1688857166896032</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>新兵营学</t>
+          <t>以梦为马</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>赵杨</t>
+          <t>张亚雪</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>zhaoyang01</t>
+          <t>zhangyaxue</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10190,12 +10175,7 @@
         <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q117" t="n">
         <v>1</v>
@@ -10237,32 +10217,32 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1688854337826427</t>
+          <t>1688856037697207</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>余梦真</t>
+          <t>齐艺欢</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>yumengzhen</t>
+          <t>qiyihuan</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10274,15 +10254,15 @@
         <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q118" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -10321,32 +10301,32 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1688856037697134</t>
+          <t>1688854292962247</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>睢佳通</t>
+          <t>翟伊蕊</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>suijiatong</t>
+          <t>zhaiyirui</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10358,11 +10338,11 @@
         <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q119" t="n">
@@ -10405,32 +10385,32 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1688854397763552</t>
+          <t>1688856003795305</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>张子涵</t>
+          <t>李鼎</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>zhangzihan03</t>
+          <t>liding02</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10439,28 +10419,13 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -10499,32 +10464,32 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1688856037696901</t>
+          <t>1688858435677635</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>逐曜先锋</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>张尧</t>
+          <t>赵庆澳</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>zhangyao02</t>
+          <t>zhaoqingao</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10536,11 +10501,11 @@
         <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q121" t="n">
@@ -10583,32 +10548,32 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1688858126859815</t>
+          <t>1688855712786442</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>晋馨贝</t>
+          <t>王福林</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>jinxinbei</t>
+          <t>wangfulin01</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -10620,7 +10585,12 @@
         <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q122" t="n">
         <v>1</v>
@@ -10662,32 +10632,32 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1688855589805868</t>
+          <t>1688855248814365</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>彭杨</t>
+          <t>徐安平</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>pengyang</t>
+          <t>xuanping</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10746,32 +10716,32 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1688856891776226</t>
+          <t>1688856037697403</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>于嘉欣</t>
+          <t>王岳</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>yujiaxin</t>
+          <t>wangyue</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10830,32 +10800,32 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1688855979803960</t>
+          <t>1688854264827950</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>驰野逐光</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>侯璐佳</t>
+          <t>赵凡骅</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>houlujia</t>
+          <t>zhaofanhua</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10914,32 +10884,32 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1688856737815887</t>
+          <t>1688854454768404</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>王佳</t>
+          <t>王同艳</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>wangjia02</t>
+          <t>wangtongyan</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -10951,12 +10921,7 @@
         <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q126" t="n">
         <v>1</v>
@@ -10998,32 +10963,32 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1688856037697337</t>
+          <t>1688857481828716</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>新兵营潇</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>康潇琼</t>
+          <t>黄成凯</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>kangxiaoqiong</t>
+          <t>huangchengkai</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11082,32 +11047,32 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1688856204843446</t>
+          <t>1688856339696430</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>新兵营潇</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>郭宜昕</t>
+          <t>刘士莹</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>guoyixin</t>
+          <t>liushiying</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11161,32 +11126,32 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1688857702013211</t>
+          <t>1688858400836966</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>新兵营学</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>焦慧瑛</t>
+          <t>李柄呈</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>jiaohuiying</t>
+          <t>libingcheng</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -11245,32 +11210,32 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1688857154905626</t>
+          <t>1688857905847066</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>新兵营潇</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>张磊磊</t>
+          <t>马艺铭</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>zhangleilei02</t>
+          <t>mayiming</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -11282,12 +11247,7 @@
         <v>1</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q130" t="n">
         <v>1</v>
@@ -11329,7 +11289,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1688856037696922</t>
+          <t>1688857792756312</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11339,22 +11299,22 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>锋芒齐聚</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>常琳洁</t>
+          <t>赵光力</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>changlinjie</t>
+          <t>zhaoguangli</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -11366,11 +11326,11 @@
         <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>7,8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q131" t="n">
@@ -11413,7 +11373,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1688854454768404</t>
+          <t>1688854662883948</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11423,22 +11383,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>王同艳</t>
+          <t>程志豪</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>wangtongyan</t>
+          <t>chengzhihao</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -11450,7 +11410,12 @@
         <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q132" t="n">
         <v>1</v>
@@ -11492,32 +11457,32 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1688857481828716</t>
+          <t>1688856037697337</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>新兵营潇</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>黄成凯</t>
+          <t>康潇琼</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>huangchengkai</t>
+          <t>kangxiaoqiong</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -11576,7 +11541,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1688857792756340</t>
+          <t>1688855623797033</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11586,22 +11551,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>王志伟</t>
+          <t>李昊</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>wangzhiwei</t>
+          <t>lihao01</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11613,7 +11578,12 @@
         <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q134" t="n">
         <v>1</v>
@@ -11655,7 +11625,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1688855795758464</t>
+          <t>1688856749818173</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11665,22 +11635,22 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>王惠惠</t>
+          <t>孙兵佳</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>wanghuihui01</t>
+          <t>sunbingjia</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -11692,12 +11662,7 @@
         <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q135" t="n">
         <v>1</v>
@@ -11739,7 +11704,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>1688855788797719</t>
+          <t>1688856725902373</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11749,22 +11714,22 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>新兵营学</t>
+          <t>新兵营恩</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>李博文</t>
+          <t>崔振</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>libowen</t>
+          <t>cuizhen01</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -11823,32 +11788,32 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1688857226802392</t>
+          <t>1688855795758382</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>新兵营恩</t>
+          <t>豫数长风</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>崔豪杰</t>
+          <t>陈慧</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>cuihaojie</t>
+          <t>chenhui</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -11860,12 +11825,7 @@
         <v>1</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q137" t="n">
         <v>1</v>
@@ -11907,32 +11867,32 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1688854397763587</t>
+          <t>1688855031888570</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>驰野逐光</t>
+          <t>骏成必燃</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>万亚朋</t>
+          <t>郭成</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>wanyapeng</t>
+          <t>guocheng</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -11991,32 +11951,32 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1688854341814383,1688855802834711</t>
+          <t>1688855788797714</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>崔朝阳</t>
+          <t>张曼玉</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>cuichaoyang</t>
+          <t>zhangmanyu</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12028,7 +11988,12 @@
         <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q139" t="n">
         <v>1</v>
@@ -12070,32 +12035,32 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1688855861872416</t>
+          <t>1688854264827893</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>驰野逐光</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>吕佳琪</t>
+          <t>尚林莹</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>lvjiaqi</t>
+          <t>shanglinying</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -12107,12 +12072,7 @@
         <v>1</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q140" t="n">
         <v>1</v>
@@ -12154,7 +12114,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1688855682772493</t>
+          <t>1688857053845851</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -12164,22 +12124,22 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>驰野逐光</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>郭雨杰</t>
+          <t>李洪仲</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>guoyujie</t>
+          <t>lihongzhong</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -12191,7 +12151,12 @@
         <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q141" t="n">
         <v>1</v>
@@ -12233,32 +12198,32 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1688855623797033</t>
+          <t>1688856339696459</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>李昊</t>
+          <t>车则龙</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>lihao01</t>
+          <t>chezelong</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -12270,12 +12235,7 @@
         <v>1</v>
       </c>
       <c r="O142" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q142" t="n">
         <v>1</v>
@@ -12317,32 +12277,32 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1688855534811567</t>
+          <t>1688856037696901</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>田硕硕</t>
+          <t>张尧</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>tianshuoshuo</t>
+          <t>zhangyao02</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -12351,28 +12311,13 @@
         </is>
       </c>
       <c r="M143" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>15,16,17,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>15,16,17,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -12411,7 +12356,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1688854264827950</t>
+          <t>1688856396700606</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12421,22 +12366,22 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>驰野逐光</t>
+          <t>同契寰宇</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>赵凡骅</t>
+          <t>和孟晴</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>zhaofanhua</t>
+          <t>hemengqing</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -12448,12 +12393,7 @@
         <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q144" t="n">
         <v>1</v>
@@ -12495,32 +12435,32 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1688855363865970</t>
+          <t>1688856891776226</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>同契破晓</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>赵怡琳</t>
+          <t>于嘉欣</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>zhaoyilin01</t>
+          <t>yujiaxin</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -12579,32 +12519,32 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1688856891776091</t>
+          <t>1688855589805868</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>新兵营潇</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>唐致鹏</t>
+          <t>彭杨</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>tangzhipeng</t>
+          <t>pengyang</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -12663,7 +12603,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1688856725902364</t>
+          <t>1688857696798168</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12673,22 +12613,22 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>骏成必燃</t>
+          <t>以梦为马</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>王怡涵</t>
+          <t>刘梦颖</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>wangyihan02</t>
+          <t>liumengying</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -12700,12 +12640,7 @@
         <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q147" t="n">
         <v>1</v>
@@ -12747,32 +12682,32 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>1688855795758468</t>
+          <t>1688856037697134</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>同契鸡公煲</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>许珂</t>
+          <t>睢佳通</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>xuke</t>
+          <t>suijiatong</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -12781,13 +12716,28 @@
         </is>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="Q148" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -12826,7 +12776,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>1688854264828019</t>
+          <t>1688856189837742</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -12836,22 +12786,22 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>超人总动员</t>
+          <t>豫数先锋</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>韩露露</t>
+          <t>薛雨</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>hanlulu</t>
+          <t>xueyu</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -12910,32 +12860,32 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1688855248814592</t>
+          <t>1688856341913737</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>以梦为马</t>
+          <t>新兵营潇</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>刘岩</t>
+          <t>高新浩</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>liuyan01</t>
+          <t>gaoxinhao</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -12944,12 +12894,7 @@
         </is>
       </c>
       <c r="M150" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -12960,12 +12905,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -13004,32 +12944,32 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>1688857359851226</t>
+          <t>1688856037696922</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>梅思莹</t>
+          <t>常琳洁</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>meisiying</t>
+          <t>changlinjie</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -13083,32 +13023,32 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1688856390786235</t>
+          <t>1688854454768334</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>新兵营恩</t>
+          <t>骏成必燃</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>刘路菲</t>
+          <t>郭家发</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>liulufei</t>
+          <t>guojiafa</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -13167,32 +13107,32 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1688858136775217</t>
+          <t>1688855534811567</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>陈浩</t>
+          <t>田硕硕</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>chenhao01</t>
+          <t>tianshuoshuo</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -13201,13 +13141,28 @@
         </is>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q153" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -13246,32 +13201,32 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1688854264827964</t>
+          <t>1688855861872416</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>驰野逐光</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>张琳琳</t>
+          <t>吕佳琪</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>zhanglinlin01</t>
+          <t>lvjiaqi</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -13283,7 +13238,12 @@
         <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q154" t="n">
         <v>1</v>
@@ -13325,32 +13285,32 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>1688856037696984</t>
+          <t>1688857704812502</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>同契鸡公煲</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>李慧婷</t>
+          <t>刘博雅</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>lihuiting</t>
+          <t>liuboya</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -13362,12 +13322,7 @@
         <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q155" t="n">
         <v>1</v>
@@ -13409,32 +13364,32 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>1688855978877650</t>
+          <t>1688856037696887</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>冯欣颖</t>
+          <t>王英颖</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>fengxinying</t>
+          <t>wangyingying03</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -13443,7 +13398,12 @@
         </is>
       </c>
       <c r="M156" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -13454,7 +13414,12 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -13493,7 +13458,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1688857166896046,1688854991811096</t>
+          <t>1688856018811331</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -13503,22 +13468,22 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>以梦为马</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>宋美璇</t>
+          <t>李浩毅</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>songmeixuan</t>
+          <t>lihaoyi</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -13577,32 +13542,32 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1688857370752824</t>
+          <t>1688858319891964</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>新兵营学</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>杜宁宁</t>
+          <t>闫月</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>duningning</t>
+          <t>yanyue01</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -13614,7 +13579,12 @@
         <v>1</v>
       </c>
       <c r="O158" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q158" t="n">
         <v>1</v>
@@ -13656,7 +13626,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1688854678837505</t>
+          <t>1688856037697032</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -13666,22 +13636,22 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>熠耀先锋</t>
+          <t>骏成必燃</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>赵赫</t>
+          <t>王晨茜</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>zhaohe</t>
+          <t>wangchenqian</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -13693,7 +13663,12 @@
         <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q159" t="n">
         <v>1</v>
@@ -13735,32 +13710,32 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1688854452775201</t>
+          <t>1688856037697290</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>新兵营恩</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>张妍</t>
+          <t>刘文苑</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>zhangyan06</t>
+          <t>liuwenyuan</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -13819,32 +13794,32 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1688856037697032</t>
+          <t>1688856204843446</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>骏成必燃</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>王晨茜</t>
+          <t>郭宜昕</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>wangchenqian</t>
+          <t>guoyixin</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -13856,15 +13831,15 @@
         <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>9,10,11,12</t>
+        </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -13903,32 +13878,32 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1688856037697207</t>
+          <t>1688856037696815</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>同契破晓</t>
+          <t>熠耀先锋</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>齐艺欢</t>
+          <t>赵毅</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>qiyihuan</t>
+          <t>zhaoyi</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -13940,20 +13915,10 @@
         <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18,19,20,21</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -13992,7 +13957,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1688858435677731</t>
+          <t>1688858020842485</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -14002,22 +13967,22 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>豫数先锋</t>
+          <t>超核先锋队</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>马平平</t>
+          <t>叶杲昂</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>mapingping</t>
+          <t>yegaoang</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -14076,7 +14041,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1688855795758409</t>
+          <t>1688857858819005</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -14086,22 +14051,22 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>胡铭</t>
+          <t>余露</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>huming</t>
+          <t>yulu</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -14155,32 +14120,32 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1688856740829087</t>
+          <t>1688854341814383,1688855802834711</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>驰野逐光</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>刘悦</t>
+          <t>崔朝阳</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>liuyue07</t>
+          <t>cuichaoyang</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -14192,11 +14157,11 @@
         <v>1</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="Q165" t="n">
@@ -14239,7 +14204,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1688855788797714</t>
+          <t>1688856891776212</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -14249,22 +14214,22 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>超核先锋队</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>张曼玉</t>
+          <t>苏志颖</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>zhangmanyu</t>
+          <t>suzhiying</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -14323,32 +14288,32 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1688855161842920</t>
+          <t>1688855954887704</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>野行逐浪</t>
+          <t>超人总动员</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>郭苏敏</t>
+          <t>姚庄蔚</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>guosumin</t>
+          <t>yaozhuangwei</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -14360,7 +14325,12 @@
         <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q167" t="n">
         <v>1</v>
@@ -14402,7 +14372,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1688858040865576</t>
+          <t>1688855979803960</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -14412,22 +14382,22 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>鸿蒙先锋</t>
+          <t>锋芒齐聚</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>苏妍</t>
+          <t>侯璐佳</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>suyan</t>
+          <t>houlujia</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -14486,32 +14456,32 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1688856390786351</t>
+          <t>1688856037697547</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>豫数长风</t>
+          <t>逐曜先锋</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>李佳慧</t>
+          <t>张佳慧</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>lijiahui03</t>
+          <t>zhangjiahui01</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -14565,32 +14535,32 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1688856037697290</t>
+          <t>1688857961849923</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>野无遗贤</t>
+          <t>鸿蒙先锋</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>刘文苑</t>
+          <t>张智博</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>liuwenyuan</t>
+          <t>zhangzhibo</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -14602,12 +14572,7 @@
         <v>1</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q170" t="n">
         <v>1</v>
@@ -14649,32 +14614,32 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1688856037696967</t>
+          <t>1688857832838680</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>骏成必燃</t>
+          <t>野无遗贤</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>刘俊杰</t>
+          <t>杜晓宁</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>liujunjie</t>
+          <t>duxiaoning</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -14733,7 +14698,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1688855712786442</t>
+          <t>1688855682772493</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -14743,22 +14708,22 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>同契寰宇</t>
+          <t>野行逐浪</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>王福林</t>
+          <t>郭雨杰</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>wangfulin01</t>
+          <t>guoyujie</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -14770,11 +14735,11 @@
         <v>1</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q172" t="n">
@@ -14867,10 +14832,10 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -14896,19 +14861,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -14931,16 +14896,16 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -14963,16 +14928,16 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="6">
@@ -15024,19 +14989,19 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
         <v>9</v>
       </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
       <c r="F7" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -15055,10 +15020,10 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="G8" t="n">
         <v>15</v>
@@ -15087,16 +15052,16 @@
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="10">
@@ -15151,10 +15116,10 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -15211,16 +15176,16 @@
         <v>41</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3658536585365854</v>
       </c>
     </row>
     <row r="14">
@@ -15243,10 +15208,10 @@
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>5</v>
@@ -15281,10 +15246,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="16">
@@ -15313,10 +15278,10 @@
         <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
@@ -15377,10 +15342,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -15431,16 +15396,16 @@
         <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9180327868852459</v>
+        <v>0.9344262295081968</v>
       </c>
       <c r="G20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>0.360655737704918</v>
+        <v>0.3934426229508197</v>
       </c>
     </row>
     <row r="21">
@@ -15463,10 +15428,10 @@
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -15555,10 +15520,10 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -15589,10 +15554,10 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="G25" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.3111111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -15622,7 +15587,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（初短二部）-7月23日</t>
+          <t>企微风灵全天在线情况通晒（初短二部）-7月24日</t>
         </is>
       </c>
     </row>
@@ -15706,10 +15671,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>2</v>
@@ -15735,19 +15700,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>6</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -15770,16 +15735,16 @@
         <v>10</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -15802,16 +15767,16 @@
         <v>8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="8">
@@ -15863,19 +15828,19 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="F9" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
@@ -15894,10 +15859,10 @@
         <v>53</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>15</v>
@@ -15926,16 +15891,16 @@
         <v>11</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="12">
@@ -15990,10 +15955,10 @@
         <v>12</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>2</v>
@@ -16050,16 +16015,16 @@
         <v>41</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3658536585365854</v>
       </c>
     </row>
     <row r="16">
@@ -16082,10 +16047,10 @@
         <v>11</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>5</v>
@@ -16120,10 +16085,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="18">
@@ -16152,10 +16117,10 @@
         <v>0.9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -16216,10 +16181,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="21">
@@ -16270,16 +16235,16 @@
         <v>61</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.9180327868852459</v>
+        <v>0.9344262295081968</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.360655737704918</v>
+        <v>0.3934426229508197</v>
       </c>
     </row>
     <row r="23">
@@ -16302,10 +16267,10 @@
         <v>10</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>1</v>
@@ -16394,10 +16359,10 @@
         <v>25</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>2</v>
@@ -16428,10 +16393,10 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.2944444444444445</v>
+        <v>0.3111111111111111</v>
       </c>
     </row>
   </sheetData>
